--- a/01_analyses_states/Chhattisgarh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Chhattisgarh/results/SoIB_summaries.xlsx
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C8">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3">

--- a/01_analyses_states/Chhattisgarh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Chhattisgarh/results/SoIB_summaries.xlsx
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C8">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3">
@@ -733,16 +733,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C2">
-        <v>71.8</v>
+        <v>75.7</v>
       </c>
       <c r="D2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E2">
-        <v>77.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -752,16 +752,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C3">
-        <v>28.2</v>
+        <v>24.3</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>22.1</v>
+        <v>20.4</v>
       </c>
     </row>
   </sheetData>
